--- a/bin/Debug/Template/LabelSDInventory.xlsx
+++ b/bin/Debug/Template/LabelSDInventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2ABBEA-327A-4352-96AA-5A5346B32B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A85E34E-51A0-4E52-AA2A-3E41FF2000ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFA5D259-3777-4AA0-9898-53B897AE17D2}"/>
+    <workbookView xWindow="2775" yWindow="2385" windowWidth="24255" windowHeight="12795" xr2:uid="{BFA5D259-3777-4AA0-9898-53B897AE17D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,10 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -82,7 +86,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -90,32 +94,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1777,67 +2055,146 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="str">
+      <c r="A1" s="10"/>
+      <c r="B1" s="11" t="str">
         <f>IF(A1&lt;&gt;"",TEXT(A1,"dd-mm-yyyy"),"")</f>
         <v/>
       </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="1:7" ht="45">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="34"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="3"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="3"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="B9" s="3"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="16"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="16"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="16"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="16"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="F14" s="3"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/bin/Debug/Template/LabelSDInventory.xlsx
+++ b/bin/Debug/Template/LabelSDInventory.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Report\LabelSDInventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A85E34E-51A0-4E52-AA2A-3E41FF2000ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D251E-34FE-4DFA-B080-BFF6BDCB2404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="2385" windowWidth="24255" windowHeight="12795" xr2:uid="{BFA5D259-3777-4AA0-9898-53B897AE17D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFA5D259-3777-4AA0-9898-53B897AE17D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,11 +28,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Date : 24-06-2026</t>
+  </si>
+  <si>
+    <t>*0001*</t>
+  </si>
+  <si>
+    <t>UL10272-26 VLT(7/0.16)(HR)AMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Rong</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -86,7 +102,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -94,307 +110,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,12 +160,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>48638</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171913</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>20266</xdr:rowOff>
+      <xdr:rowOff>51110</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1721617" cy="172639"/>
+    <xdr:ext cx="1226635" cy="172639"/>
     <xdr:sp macro="" textlink="$B$1">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -436,8 +179,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="48638" y="20266"/>
-          <a:ext cx="1721617" cy="172639"/>
+          <a:off x="3215267" y="51110"/>
+          <a:ext cx="1226635" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -475,7 +218,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t> </a:t>
+            <a:t>Date : 24-06-2026</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1100" b="1">
             <a:solidFill>
@@ -549,9 +292,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
+      <xdr:colOff>4645</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150567</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="482202" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -567,7 +310,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1125140"/>
+          <a:off x="4645" y="1293567"/>
           <a:ext cx="482202" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -610,7 +353,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
+      <xdr:rowOff>52993</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="654844" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -626,7 +369,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1344215"/>
+          <a:off x="0" y="1576993"/>
           <a:ext cx="654844" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -657,7 +400,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
-            <a:t>RM Des</a:t>
+            <a:t>RM 	</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -667,9 +410,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>4647</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
+      <xdr:rowOff>145917</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="654844" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -685,7 +428,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1563290"/>
+          <a:off x="4647" y="1860417"/>
           <a:ext cx="654844" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -726,9 +469,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>321469</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
+      <xdr:colOff>326114</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150567</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="160735" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -744,7 +487,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="588169" y="1125140"/>
+          <a:off x="934785" y="1293567"/>
           <a:ext cx="160735" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -787,7 +530,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>321469</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
+      <xdr:rowOff>52993</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="160735" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -803,7 +546,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="588169" y="1344215"/>
+          <a:off x="930140" y="1576993"/>
           <a:ext cx="160735" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -844,9 +587,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>321469</xdr:colOff>
+      <xdr:colOff>326116</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>23811</xdr:rowOff>
+      <xdr:rowOff>158548</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="160735" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -862,7 +605,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="588169" y="1557336"/>
+          <a:off x="934787" y="1873048"/>
           <a:ext cx="160735" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -905,7 +648,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>500063</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
+      <xdr:rowOff>52993</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2500312" cy="172639"/>
     <xdr:sp macro="" textlink="$B$7">
@@ -921,7 +664,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="766763" y="1344215"/>
+          <a:off x="1108734" y="1576993"/>
           <a:ext cx="2500312" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -960,7 +703,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t> </a:t>
+            <a:t>UL10272-26 VLT(7/0.16)(HR)AMP</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1100" b="0">
             <a:solidFill>
@@ -977,20 +720,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>29764</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>11906</xdr:rowOff>
+      <xdr:rowOff>188446</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>575830</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152726</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="Group 13">
+        <xdr:cNvPr id="3" name="Group 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBD452CF-A404-45BF-88C1-87556C886640}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D9B4EA5-75CB-62F9-C8A2-6CD3535FE817}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -998,10 +741,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="29764" y="2488406"/>
-          <a:ext cx="4198090" cy="726281"/>
-          <a:chOff x="95250" y="2684860"/>
-          <a:chExt cx="3482578" cy="779859"/>
+          <a:off x="29764" y="2664946"/>
+          <a:ext cx="4198090" cy="726280"/>
+          <a:chOff x="29764" y="2660314"/>
+          <a:chExt cx="4198090" cy="726280"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -1017,8 +760,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="95250" y="2684860"/>
-            <a:ext cx="1160859" cy="214313"/>
+            <a:off x="29764" y="2660314"/>
+            <a:ext cx="1399363" cy="199589"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1075,8 +818,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1256109" y="2684860"/>
-            <a:ext cx="1160859" cy="214313"/>
+            <a:off x="1429127" y="2660318"/>
+            <a:ext cx="1399363" cy="199589"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1133,8 +876,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2416969" y="2684860"/>
-            <a:ext cx="1160859" cy="214313"/>
+            <a:off x="2828491" y="2660314"/>
+            <a:ext cx="1399363" cy="199589"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1191,8 +934,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="95250" y="2899172"/>
-            <a:ext cx="1160859" cy="565547"/>
+            <a:off x="29764" y="2859902"/>
+            <a:ext cx="1399363" cy="526692"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1246,8 +989,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1256109" y="2899172"/>
-            <a:ext cx="1160859" cy="565547"/>
+            <a:off x="1429127" y="2859902"/>
+            <a:ext cx="1399363" cy="526692"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1301,8 +1044,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2416969" y="2899172"/>
-            <a:ext cx="1160859" cy="565547"/>
+            <a:off x="2828491" y="2859902"/>
+            <a:ext cx="1399363" cy="526692"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1350,8 +1093,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>25119</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>52991</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="813110" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -1367,7 +1110,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1739619"/>
+          <a:off x="0" y="2148491"/>
           <a:ext cx="813110" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1408,9 +1151,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>321469</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>28457</xdr:rowOff>
+      <xdr:colOff>326115</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>60975</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="160735" cy="172639"/>
     <xdr:sp macro="" textlink="">
@@ -1426,7 +1169,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="930140" y="1742957"/>
+          <a:off x="934786" y="2156475"/>
           <a:ext cx="160735" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1467,9 +1210,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>509356</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>11140</xdr:rowOff>
+      <xdr:colOff>514003</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>52952</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2500312" cy="172639"/>
     <xdr:sp macro="" textlink="$B$9">
@@ -1485,7 +1228,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1119822" y="1725640"/>
+          <a:off x="1122674" y="2148452"/>
           <a:ext cx="2500312" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1524,7 +1267,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t> </a:t>
+            <a:t>1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1100" b="0">
             <a:solidFill>
@@ -1596,7 +1339,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t> </a:t>
+            <a:t>  Rong</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1400" b="0">
             <a:solidFill>
@@ -1611,9 +1354,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>504391</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25435</xdr:rowOff>
+      <xdr:colOff>509036</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>146237</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2500312" cy="172639"/>
     <xdr:sp macro="" textlink="$B$6">
@@ -1629,7 +1372,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1114857" y="1168435"/>
+          <a:off x="1117707" y="1289237"/>
           <a:ext cx="2500312" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1668,7 +1411,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t> </a:t>
+            <a:t>3048</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1100" b="0">
             <a:solidFill>
@@ -1683,9 +1426,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>504394</xdr:colOff>
+      <xdr:colOff>509041</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>12447</xdr:rowOff>
+      <xdr:rowOff>147184</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2500312" cy="172639"/>
     <xdr:sp macro="" textlink="$B$8">
@@ -1701,7 +1444,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1114860" y="1536447"/>
+          <a:off x="1117712" y="1861684"/>
           <a:ext cx="2500312" cy="172639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1740,7 +1483,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t> </a:t>
+            <a:t>0</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1100" b="0">
             <a:solidFill>
@@ -2059,142 +1802,155 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="10"/>
-      <c r="B1" s="11" t="str">
-        <f>IF(A1&lt;&gt;"",TEXT(A1,"dd-mm-yyyy"),"")</f>
-        <v/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="13"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="15"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="45">
-      <c r="A4" s="31"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="32"/>
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="34"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="16"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="9">
+        <v>3048</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="17"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="18"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="19"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="20"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="19"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="18"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="19"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="16"/>
+      <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="17"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="16"/>
+      <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="17"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="16"/>
+      <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="17"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="16"/>
+      <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="17"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="16"/>
+      <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="23"/>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
